--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:27:54+00:00</t>
+    <t>2023-04-26T14:43:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T14:43:04+00:00</t>
+    <t>2023-04-27T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T16:49:23+00:00</t>
+    <t>2023-05-02T12:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T12:59:07+00:00</t>
+    <t>2023-05-02T13:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T13:06:55+00:00</t>
+    <t>2023-05-02T14:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:33:57+00:00</t>
+    <t>2023-07-18T09:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:12+00:00</t>
+    <t>2023-07-18T09:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:49+00:00</t>
+    <t>2023-07-18T09:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4792" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4791" uniqueCount="661">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:37:51+00:00</t>
+    <t>2023-09-19T16:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -143,6 +143,10 @@
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
   </si>
   <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
+  </si>
+  <si>
     <t>Event</t>
   </si>
   <si>
@@ -561,7 +565,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -648,7 +652,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -1117,7 +1121,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1175,7 +1179,7 @@
     <t>Often just a dateTime for Vital Signs.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -1210,7 +1214,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1260,7 +1264,7 @@
     <t>Vital Signs value are recorded using the Quantity data type. For supporting observations such as Cuff size could use other datatypes such as CodeableConcept.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>9. SHALL contain exactly one [1..1] value with @xsi:type="PQ" (CONF:7305).</t>
@@ -1531,10 +1535,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://www.interopsante.org/fhir/structuredefinition/observation/fr-obervation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1584,7 +1585,7 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1946,7 +1947,7 @@
     <t>Used when reporting vital signs panel components.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1968,7 +1969,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1980,7 +1981,7 @@
     <t>Used when reporting systolic and diastolic blood pressure.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
@@ -2037,7 +2038,7 @@
     <t>Vital Sign Value recorded with UCUM.</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Common UCUM units for recording Vital Signs.</t>
@@ -2073,7 +2074,7 @@
     <t>Observation.component.interpretation</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2531,19 +2532,19 @@
         <v>36</v>
       </c>
       <c r="AJ1" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AK1" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AL1" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AM1" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AN1" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AO1" t="s" s="2">
         <v>36</v>
@@ -2554,10 +2555,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2568,7 +2569,7 @@
         <v>34</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>36</v>
@@ -2577,19 +2578,19 @@
         <v>36</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2639,13 +2640,13 @@
         <v>36</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>36</v>
@@ -2674,10 +2675,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2688,7 +2689,7 @@
         <v>34</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>36</v>
@@ -2697,16 +2698,16 @@
         <v>36</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -2757,19 +2758,19 @@
         <v>36</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="s" s="2">
         <v>36</v>
@@ -2781,7 +2782,7 @@
         <v>36</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO3" t="s" s="2">
         <v>36</v>
@@ -2792,10 +2793,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2806,7 +2807,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>36</v>
@@ -2818,13 +2819,13 @@
         <v>36</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2875,13 +2876,13 @@
         <v>36</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>36</v>
@@ -2899,7 +2900,7 @@
         <v>36</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>36</v>
@@ -2910,14 +2911,14 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -2936,16 +2937,16 @@
         <v>36</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2983,19 +2984,19 @@
         <v>36</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>34</v>
@@ -3004,10 +3005,10 @@
         <v>35</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>36</v>
@@ -3019,7 +3020,7 @@
         <v>36</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>36</v>
@@ -3030,10 +3031,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -3044,7 +3045,7 @@
         <v>34</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>36</v>
@@ -3053,19 +3054,19 @@
         <v>36</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3115,19 +3116,19 @@
         <v>36</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>36</v>
@@ -3139,7 +3140,7 @@
         <v>36</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>36</v>
@@ -3150,10 +3151,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3164,7 +3165,7 @@
         <v>34</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>36</v>
@@ -3173,19 +3174,19 @@
         <v>36</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3235,19 +3236,19 @@
         <v>36</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>36</v>
@@ -3259,7 +3260,7 @@
         <v>36</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>36</v>
@@ -3270,10 +3271,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3284,7 +3285,7 @@
         <v>34</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>36</v>
@@ -3293,19 +3294,19 @@
         <v>36</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3355,19 +3356,19 @@
         <v>36</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>36</v>
@@ -3379,7 +3380,7 @@
         <v>36</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>36</v>
@@ -3390,10 +3391,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3413,19 +3414,19 @@
         <v>36</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3475,7 +3476,7 @@
         <v>36</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>34</v>
@@ -3484,10 +3485,10 @@
         <v>35</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>36</v>
@@ -3499,7 +3500,7 @@
         <v>36</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>36</v>
@@ -3510,10 +3511,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3533,19 +3534,19 @@
         <v>36</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3571,13 +3572,13 @@
         <v>36</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>36</v>
@@ -3595,7 +3596,7 @@
         <v>36</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>34</v>
@@ -3604,10 +3605,10 @@
         <v>35</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>36</v>
@@ -3616,10 +3617,10 @@
         <v>36</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>36</v>
@@ -3630,10 +3631,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3653,19 +3654,19 @@
         <v>36</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3691,13 +3692,13 @@
         <v>36</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>36</v>
@@ -3715,7 +3716,7 @@
         <v>36</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>34</v>
@@ -3724,10 +3725,10 @@
         <v>35</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>36</v>
@@ -3736,10 +3737,10 @@
         <v>36</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>36</v>
@@ -3750,10 +3751,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3764,28 +3765,28 @@
         <v>34</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3835,19 +3836,19 @@
         <v>36</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>36</v>
@@ -3859,7 +3860,7 @@
         <v>36</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>36</v>
@@ -3870,10 +3871,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3884,7 +3885,7 @@
         <v>34</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>36</v>
@@ -3896,16 +3897,16 @@
         <v>36</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3931,13 +3932,13 @@
         <v>36</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>36</v>
@@ -3955,19 +3956,19 @@
         <v>36</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>36</v>
@@ -3979,7 +3980,7 @@
         <v>36</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>36</v>
@@ -3990,21 +3991,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>36</v>
@@ -4016,16 +4017,16 @@
         <v>36</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4075,19 +4076,19 @@
         <v>36</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>36</v>
@@ -4099,7 +4100,7 @@
         <v>36</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>36</v>
@@ -4110,14 +4111,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4136,16 +4137,16 @@
         <v>36</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4195,7 +4196,7 @@
         <v>36</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>34</v>
@@ -4219,7 +4220,7 @@
         <v>36</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>36</v>
@@ -4230,14 +4231,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4256,16 +4257,16 @@
         <v>36</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4303,19 +4304,19 @@
         <v>36</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>34</v>
@@ -4324,10 +4325,10 @@
         <v>35</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>36</v>
@@ -4339,7 +4340,7 @@
         <v>36</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>36</v>
@@ -4350,13 +4351,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>36</v>
@@ -4366,7 +4367,7 @@
         <v>34</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>36</v>
@@ -4378,13 +4379,13 @@
         <v>36</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4435,7 +4436,7 @@
         <v>36</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>34</v>
@@ -4444,10 +4445,10 @@
         <v>35</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>36</v>
@@ -4459,7 +4460,7 @@
         <v>36</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>36</v>
@@ -4470,13 +4471,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>36</v>
@@ -4486,7 +4487,7 @@
         <v>34</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>36</v>
@@ -4498,13 +4499,13 @@
         <v>36</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4555,7 +4556,7 @@
         <v>36</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>34</v>
@@ -4564,10 +4565,10 @@
         <v>35</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>36</v>
@@ -4579,7 +4580,7 @@
         <v>36</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>36</v>
@@ -4590,26 +4591,26 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>36</v>
@@ -4618,16 +4619,16 @@
         <v>36</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4677,7 +4678,7 @@
         <v>36</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>34</v>
@@ -4686,10 +4687,10 @@
         <v>35</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>36</v>
@@ -4701,7 +4702,7 @@
         <v>36</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>36</v>
@@ -4712,13 +4713,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>36</v>
@@ -4728,7 +4729,7 @@
         <v>34</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>36</v>
@@ -4740,13 +4741,13 @@
         <v>36</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4797,7 +4798,7 @@
         <v>36</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>34</v>
@@ -4806,10 +4807,10 @@
         <v>35</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>36</v>
@@ -4832,14 +4833,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4852,25 +4853,25 @@
         <v>36</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>36</v>
@@ -4907,19 +4908,19 @@
         <v>36</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>34</v>
@@ -4928,10 +4929,10 @@
         <v>35</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>36</v>
@@ -4943,7 +4944,7 @@
         <v>36</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>36</v>
@@ -4954,10 +4955,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4977,20 +4978,20 @@
         <v>36</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>36</v>
@@ -5039,7 +5040,7 @@
         <v>36</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>34</v>
@@ -5048,25 +5049,25 @@
         <v>35</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>36</v>
@@ -5074,14 +5075,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5097,22 +5098,22 @@
         <v>36</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>36</v>
@@ -5161,7 +5162,7 @@
         <v>36</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>34</v>
@@ -5170,22 +5171,22 @@
         <v>35</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>36</v>
@@ -5196,14 +5197,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5219,19 +5220,19 @@
         <v>36</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5281,7 +5282,7 @@
         <v>36</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>34</v>
@@ -5290,22 +5291,22 @@
         <v>35</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>36</v>
@@ -5316,10 +5317,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5327,34 +5328,34 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>36</v>
@@ -5379,13 +5380,13 @@
         <v>36</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>36</v>
@@ -5403,34 +5404,34 @@
         <v>36</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>36</v>
@@ -5438,10 +5439,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5449,13 +5450,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>36</v>
@@ -5464,19 +5465,19 @@
         <v>36</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>36</v>
@@ -5501,29 +5502,29 @@
         <v>36</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>34</v>
@@ -5532,10 +5533,10 @@
         <v>35</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>36</v>
@@ -5544,13 +5545,13 @@
         <v>36</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>36</v>
@@ -5558,26 +5559,26 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>36</v>
@@ -5586,19 +5587,19 @@
         <v>36</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>36</v>
@@ -5623,13 +5624,13 @@
         <v>36</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>36</v>
@@ -5647,7 +5648,7 @@
         <v>36</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>34</v>
@@ -5656,10 +5657,10 @@
         <v>35</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>36</v>
@@ -5668,13 +5669,13 @@
         <v>36</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>36</v>
@@ -5682,10 +5683,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5696,7 +5697,7 @@
         <v>34</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>36</v>
@@ -5708,13 +5709,13 @@
         <v>36</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5765,13 +5766,13 @@
         <v>36</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>36</v>
@@ -5789,7 +5790,7 @@
         <v>36</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>36</v>
@@ -5800,14 +5801,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5826,16 +5827,16 @@
         <v>36</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5873,19 +5874,19 @@
         <v>36</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>34</v>
@@ -5894,10 +5895,10 @@
         <v>35</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>36</v>
@@ -5909,7 +5910,7 @@
         <v>36</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>36</v>
@@ -5920,10 +5921,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5931,34 +5932,34 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>36</v>
@@ -6007,7 +6008,7 @@
         <v>36</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>34</v>
@@ -6016,10 +6017,10 @@
         <v>35</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>36</v>
@@ -6028,10 +6029,10 @@
         <v>36</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>36</v>
@@ -6042,10 +6043,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6056,7 +6057,7 @@
         <v>34</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>36</v>
@@ -6068,13 +6069,13 @@
         <v>36</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6125,13 +6126,13 @@
         <v>36</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>36</v>
@@ -6149,7 +6150,7 @@
         <v>36</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>36</v>
@@ -6160,14 +6161,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6186,16 +6187,16 @@
         <v>36</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6233,19 +6234,19 @@
         <v>36</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>34</v>
@@ -6254,10 +6255,10 @@
         <v>35</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>36</v>
@@ -6269,7 +6270,7 @@
         <v>36</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>36</v>
@@ -6280,10 +6281,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6291,41 +6292,41 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>36</v>
@@ -6367,19 +6368,19 @@
         <v>36</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>36</v>
@@ -6388,10 +6389,10 @@
         <v>36</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>36</v>
@@ -6402,10 +6403,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6416,7 +6417,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>36</v>
@@ -6425,19 +6426,19 @@
         <v>36</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6487,19 +6488,19 @@
         <v>36</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>36</v>
@@ -6508,10 +6509,10 @@
         <v>36</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>36</v>
@@ -6522,10 +6523,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6533,41 +6534,41 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>36</v>
@@ -6609,19 +6610,19 @@
         <v>36</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>36</v>
@@ -6630,10 +6631,10 @@
         <v>36</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>36</v>
@@ -6644,10 +6645,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6658,7 +6659,7 @@
         <v>34</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>36</v>
@@ -6667,22 +6668,22 @@
         <v>36</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>36</v>
@@ -6731,19 +6732,19 @@
         <v>36</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>36</v>
@@ -6752,10 +6753,10 @@
         <v>36</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>36</v>
@@ -6766,10 +6767,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6780,7 +6781,7 @@
         <v>34</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>36</v>
@@ -6789,22 +6790,22 @@
         <v>36</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>36</v>
@@ -6853,19 +6854,19 @@
         <v>36</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>36</v>
@@ -6874,10 +6875,10 @@
         <v>36</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>36</v>
@@ -6888,10 +6889,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6902,7 +6903,7 @@
         <v>34</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>36</v>
@@ -6911,22 +6912,22 @@
         <v>36</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>36</v>
@@ -6975,19 +6976,19 @@
         <v>36</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>36</v>
@@ -6996,10 +6997,10 @@
         <v>36</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>36</v>
@@ -7010,45 +7011,45 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>36</v>
@@ -7073,13 +7074,13 @@
         <v>36</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>36</v>
@@ -7097,45 +7098,45 @@
         <v>36</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7146,7 +7147,7 @@
         <v>34</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>36</v>
@@ -7158,13 +7159,13 @@
         <v>36</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7215,13 +7216,13 @@
         <v>36</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>36</v>
@@ -7239,7 +7240,7 @@
         <v>36</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>36</v>
@@ -7250,14 +7251,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7276,16 +7277,16 @@
         <v>36</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7323,19 +7324,19 @@
         <v>36</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>34</v>
@@ -7344,10 +7345,10 @@
         <v>35</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>36</v>
@@ -7359,7 +7360,7 @@
         <v>36</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>36</v>
@@ -7370,10 +7371,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7393,22 +7394,22 @@
         <v>36</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>36</v>
@@ -7445,17 +7446,17 @@
         <v>36</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>34</v>
@@ -7464,10 +7465,10 @@
         <v>35</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>36</v>
@@ -7476,10 +7477,10 @@
         <v>36</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>36</v>
@@ -7490,23 +7491,23 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>36</v>
@@ -7515,22 +7516,22 @@
         <v>36</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>36</v>
@@ -7579,7 +7580,7 @@
         <v>36</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>34</v>
@@ -7588,10 +7589,10 @@
         <v>35</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>36</v>
@@ -7600,10 +7601,10 @@
         <v>36</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>36</v>
@@ -7614,10 +7615,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7628,7 +7629,7 @@
         <v>34</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>36</v>
@@ -7640,13 +7641,13 @@
         <v>36</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7697,13 +7698,13 @@
         <v>36</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>36</v>
@@ -7721,7 +7722,7 @@
         <v>36</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>36</v>
@@ -7732,14 +7733,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7758,16 +7759,16 @@
         <v>36</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7805,19 +7806,19 @@
         <v>36</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>34</v>
@@ -7826,10 +7827,10 @@
         <v>35</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>36</v>
@@ -7841,7 +7842,7 @@
         <v>36</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>36</v>
@@ -7852,10 +7853,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7863,10 +7864,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>36</v>
@@ -7875,29 +7876,29 @@
         <v>36</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>36</v>
@@ -7939,19 +7940,19 @@
         <v>36</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>36</v>
@@ -7960,10 +7961,10 @@
         <v>36</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>36</v>
@@ -7974,10 +7975,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7988,7 +7989,7 @@
         <v>34</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>36</v>
@@ -7997,19 +7998,19 @@
         <v>36</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8059,19 +8060,19 @@
         <v>36</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>36</v>
@@ -8080,10 +8081,10 @@
         <v>36</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>36</v>
@@ -8094,10 +8095,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8105,10 +8106,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>36</v>
@@ -8117,29 +8118,29 @@
         <v>36</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>36</v>
@@ -8181,19 +8182,19 @@
         <v>36</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>36</v>
@@ -8202,10 +8203,10 @@
         <v>36</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>36</v>
@@ -8216,10 +8217,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8230,7 +8231,7 @@
         <v>34</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>36</v>
@@ -8239,22 +8240,22 @@
         <v>36</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>36</v>
@@ -8303,19 +8304,19 @@
         <v>36</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>36</v>
@@ -8324,10 +8325,10 @@
         <v>36</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>36</v>
@@ -8338,10 +8339,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8352,7 +8353,7 @@
         <v>34</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>36</v>
@@ -8361,22 +8362,22 @@
         <v>36</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>36</v>
@@ -8425,19 +8426,19 @@
         <v>36</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>36</v>
@@ -8446,10 +8447,10 @@
         <v>36</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>36</v>
@@ -8460,10 +8461,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8474,7 +8475,7 @@
         <v>34</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>36</v>
@@ -8483,22 +8484,22 @@
         <v>36</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>36</v>
@@ -8547,19 +8548,19 @@
         <v>36</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>36</v>
@@ -8568,10 +8569,10 @@
         <v>36</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>36</v>
@@ -8582,10 +8583,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8593,34 +8594,34 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>36</v>
@@ -8669,34 +8670,34 @@
         <v>36</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>36</v>
@@ -8704,10 +8705,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8727,19 +8728,19 @@
         <v>36</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8789,7 +8790,7 @@
         <v>36</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>34</v>
@@ -8798,10 +8799,10 @@
         <v>35</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>36</v>
@@ -8810,13 +8811,13 @@
         <v>36</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>36</v>
@@ -8824,21 +8825,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>36</v>
@@ -8847,22 +8848,22 @@
         <v>36</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>36</v>
@@ -8911,34 +8912,34 @@
         <v>36</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>36</v>
@@ -8946,45 +8947,45 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>36</v>
@@ -9033,34 +9034,34 @@
         <v>36</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>36</v>
@@ -9068,10 +9069,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9082,7 +9083,7 @@
         <v>34</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>36</v>
@@ -9091,19 +9092,19 @@
         <v>36</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9153,19 +9154,19 @@
         <v>36</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>36</v>
@@ -9174,13 +9175,13 @@
         <v>36</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>36</v>
@@ -9188,10 +9189,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9211,22 +9212,22 @@
         <v>36</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>36</v>
@@ -9275,7 +9276,7 @@
         <v>36</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>34</v>
@@ -9284,25 +9285,25 @@
         <v>35</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>36</v>
@@ -9310,10 +9311,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9324,31 +9325,31 @@
         <v>34</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>36</v>
@@ -9385,58 +9386,58 @@
         <v>36</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>36</v>
@@ -9446,31 +9447,31 @@
         <v>34</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>36</v>
@@ -9519,45 +9520,45 @@
         <v>36</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9568,7 +9569,7 @@
         <v>34</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>36</v>
@@ -9580,13 +9581,13 @@
         <v>36</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9637,13 +9638,13 @@
         <v>36</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>36</v>
@@ -9661,7 +9662,7 @@
         <v>36</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>36</v>
@@ -9672,14 +9673,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9698,16 +9699,16 @@
         <v>36</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9745,19 +9746,19 @@
         <v>36</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>34</v>
@@ -9766,10 +9767,10 @@
         <v>35</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>36</v>
@@ -9781,7 +9782,7 @@
         <v>36</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>36</v>
@@ -9792,10 +9793,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9803,34 +9804,34 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>36</v>
@@ -9879,19 +9880,19 @@
         <v>36</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>36</v>
@@ -9900,10 +9901,10 @@
         <v>36</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>36</v>
@@ -9914,10 +9915,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9928,37 +9929,37 @@
         <v>34</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>36</v>
@@ -9979,13 +9980,13 @@
         <v>36</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>36</v>
@@ -10003,19 +10004,19 @@
         <v>36</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>36</v>
@@ -10024,10 +10025,10 @@
         <v>36</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>36</v>
@@ -10038,10 +10039,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10049,34 +10050,34 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>36</v>
@@ -10125,19 +10126,19 @@
         <v>36</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>36</v>
@@ -10146,10 +10147,10 @@
         <v>36</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>36</v>
@@ -10160,10 +10161,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10171,41 +10172,41 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>36</v>
@@ -10247,19 +10248,19 @@
         <v>36</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>36</v>
@@ -10268,10 +10269,10 @@
         <v>36</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>36</v>
@@ -10282,10 +10283,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10293,41 +10294,41 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>36</v>
@@ -10369,19 +10370,19 @@
         <v>36</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>36</v>
@@ -10390,10 +10391,10 @@
         <v>36</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>36</v>
@@ -10404,10 +10405,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10418,10 +10419,10 @@
         <v>34</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>36</v>
@@ -10430,19 +10431,19 @@
         <v>36</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>36</v>
@@ -10467,13 +10468,13 @@
         <v>36</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>36</v>
@@ -10491,19 +10492,19 @@
         <v>36</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>36</v>
@@ -10512,10 +10513,10 @@
         <v>36</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>36</v>
@@ -10526,10 +10527,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10540,7 +10541,7 @@
         <v>34</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>36</v>
@@ -10552,13 +10553,13 @@
         <v>36</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10609,13 +10610,13 @@
         <v>36</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>36</v>
@@ -10633,7 +10634,7 @@
         <v>36</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>36</v>
@@ -10644,14 +10645,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10670,16 +10671,16 @@
         <v>36</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10717,19 +10718,19 @@
         <v>36</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>34</v>
@@ -10738,10 +10739,10 @@
         <v>35</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>36</v>
@@ -10753,7 +10754,7 @@
         <v>36</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>36</v>
@@ -10764,10 +10765,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10787,22 +10788,22 @@
         <v>36</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>36</v>
@@ -10851,7 +10852,7 @@
         <v>36</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>34</v>
@@ -10860,10 +10861,10 @@
         <v>35</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>36</v>
@@ -10872,10 +10873,10 @@
         <v>36</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>36</v>
@@ -10886,10 +10887,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10900,7 +10901,7 @@
         <v>34</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>36</v>
@@ -10912,13 +10913,13 @@
         <v>36</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10969,13 +10970,13 @@
         <v>36</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>36</v>
@@ -10993,7 +10994,7 @@
         <v>36</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>36</v>
@@ -11004,14 +11005,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11030,16 +11031,16 @@
         <v>36</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11077,19 +11078,19 @@
         <v>36</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>34</v>
@@ -11098,10 +11099,10 @@
         <v>35</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>36</v>
@@ -11113,7 +11114,7 @@
         <v>36</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>36</v>
@@ -11124,10 +11125,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11135,10 +11136,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>36</v>
@@ -11147,22 +11148,22 @@
         <v>36</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>36</v>
@@ -11211,19 +11212,19 @@
         <v>36</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>36</v>
@@ -11232,10 +11233,10 @@
         <v>36</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>36</v>
@@ -11246,10 +11247,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11260,7 +11261,7 @@
         <v>34</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>36</v>
@@ -11269,19 +11270,19 @@
         <v>36</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11331,19 +11332,19 @@
         <v>36</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>36</v>
@@ -11352,10 +11353,10 @@
         <v>36</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>36</v>
@@ -11366,10 +11367,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11377,10 +11378,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>36</v>
@@ -11389,22 +11390,22 @@
         <v>36</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>36</v>
@@ -11453,19 +11454,19 @@
         <v>36</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>36</v>
@@ -11474,10 +11475,10 @@
         <v>36</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>36</v>
@@ -11488,10 +11489,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11502,7 +11503,7 @@
         <v>34</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>36</v>
@@ -11511,22 +11512,22 @@
         <v>36</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>36</v>
@@ -11575,19 +11576,19 @@
         <v>36</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>36</v>
@@ -11596,10 +11597,10 @@
         <v>36</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>36</v>
@@ -11610,10 +11611,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11624,7 +11625,7 @@
         <v>34</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>36</v>
@@ -11633,22 +11634,22 @@
         <v>36</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>36</v>
@@ -11697,19 +11698,19 @@
         <v>36</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>36</v>
@@ -11718,10 +11719,10 @@
         <v>36</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>36</v>
@@ -11732,10 +11733,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11746,7 +11747,7 @@
         <v>34</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>36</v>
@@ -11755,22 +11756,22 @@
         <v>36</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>36</v>
@@ -11819,19 +11820,19 @@
         <v>36</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>36</v>
@@ -11840,10 +11841,10 @@
         <v>36</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>36</v>
@@ -11854,14 +11855,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11880,19 +11881,19 @@
         <v>36</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>36</v>
@@ -11917,11 +11918,9 @@
         <v>36</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
         <v>487</v>
       </c>
@@ -11941,7 +11940,7 @@
         <v>36</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>34</v>
@@ -11950,10 +11949,10 @@
         <v>35</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>36</v>
@@ -12072,10 +12071,10 @@
         <v>35</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>36</v>
@@ -12112,7 +12111,7 @@
         <v>34</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>36</v>
@@ -12124,7 +12123,7 @@
         <v>36</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>501</v>
@@ -12159,7 +12158,7 @@
         <v>36</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y81" t="s" s="2">
         <v>504</v>
@@ -12189,13 +12188,13 @@
         <v>34</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>36</v>
@@ -12232,7 +12231,7 @@
         <v>34</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>36</v>
@@ -12244,13 +12243,13 @@
         <v>36</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12301,13 +12300,13 @@
         <v>36</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>36</v>
@@ -12325,7 +12324,7 @@
         <v>36</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>36</v>
@@ -12343,7 +12342,7 @@
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12362,16 +12361,16 @@
         <v>36</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12409,19 +12408,19 @@
         <v>36</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>34</v>
@@ -12430,10 +12429,10 @@
         <v>35</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>36</v>
@@ -12445,7 +12444,7 @@
         <v>36</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>36</v>
@@ -12479,22 +12478,22 @@
         <v>36</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>36</v>
@@ -12519,7 +12518,7 @@
         <v>36</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
@@ -12541,7 +12540,7 @@
         <v>36</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>34</v>
@@ -12550,10 +12549,10 @@
         <v>35</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>36</v>
@@ -12562,10 +12561,10 @@
         <v>36</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>36</v>
@@ -12590,7 +12589,7 @@
         <v>34</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>36</v>
@@ -12599,22 +12598,22 @@
         <v>36</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>36</v>
@@ -12663,19 +12662,19 @@
         <v>36</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>36</v>
@@ -12684,10 +12683,10 @@
         <v>36</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>36</v>
@@ -12712,7 +12711,7 @@
         <v>34</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>36</v>
@@ -12724,7 +12723,7 @@
         <v>36</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>516</v>
@@ -12761,7 +12760,7 @@
         <v>36</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y86" t="s" s="2">
         <v>519</v>
@@ -12791,13 +12790,13 @@
         <v>34</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>36</v>
@@ -12834,7 +12833,7 @@
         <v>34</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>36</v>
@@ -12846,13 +12845,13 @@
         <v>36</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12903,13 +12902,13 @@
         <v>36</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>36</v>
@@ -12927,7 +12926,7 @@
         <v>36</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>36</v>
@@ -12945,7 +12944,7 @@
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12964,16 +12963,16 @@
         <v>36</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13011,19 +13010,19 @@
         <v>36</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>34</v>
@@ -13032,10 +13031,10 @@
         <v>35</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>36</v>
@@ -13047,7 +13046,7 @@
         <v>36</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>36</v>
@@ -13081,22 +13080,22 @@
         <v>36</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>36</v>
@@ -13121,7 +13120,7 @@
         <v>36</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
@@ -13143,7 +13142,7 @@
         <v>36</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>34</v>
@@ -13152,10 +13151,10 @@
         <v>35</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>36</v>
@@ -13164,10 +13163,10 @@
         <v>36</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>36</v>
@@ -13192,7 +13191,7 @@
         <v>34</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>36</v>
@@ -13201,22 +13200,22 @@
         <v>36</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>36</v>
@@ -13265,19 +13264,19 @@
         <v>36</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>36</v>
@@ -13286,10 +13285,10 @@
         <v>36</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>36</v>
@@ -13314,7 +13313,7 @@
         <v>34</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>36</v>
@@ -13391,13 +13390,13 @@
         <v>34</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>36</v>
@@ -13434,7 +13433,7 @@
         <v>34</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>36</v>
@@ -13511,13 +13510,13 @@
         <v>34</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>36</v>
@@ -13636,7 +13635,7 @@
         <v>35</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>551</v>
@@ -13676,7 +13675,7 @@
         <v>34</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>36</v>
@@ -13688,13 +13687,13 @@
         <v>36</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13745,13 +13744,13 @@
         <v>36</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>36</v>
@@ -13769,7 +13768,7 @@
         <v>36</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>36</v>
@@ -13787,7 +13786,7 @@
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13806,16 +13805,16 @@
         <v>36</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13853,19 +13852,19 @@
         <v>36</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>34</v>
@@ -13874,10 +13873,10 @@
         <v>35</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>36</v>
@@ -13889,7 +13888,7 @@
         <v>36</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>36</v>
@@ -13920,13 +13919,13 @@
         <v>36</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L96" t="s" s="2">
         <v>558</v>
@@ -13935,10 +13934,10 @@
         <v>559</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>36</v>
@@ -13996,10 +13995,10 @@
         <v>35</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>36</v>
@@ -14011,7 +14010,7 @@
         <v>36</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>36</v>
@@ -14036,7 +14035,7 @@
         <v>34</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>36</v>
@@ -14113,7 +14112,7 @@
         <v>34</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>566</v>
@@ -14156,7 +14155,7 @@
         <v>34</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>36</v>
@@ -14233,7 +14232,7 @@
         <v>34</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>566</v>
@@ -14276,7 +14275,7 @@
         <v>34</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>36</v>
@@ -14288,7 +14287,7 @@
         <v>36</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L99" t="s" s="2">
         <v>575</v>
@@ -14325,7 +14324,7 @@
         <v>36</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y99" t="s" s="2">
         <v>579</v>
@@ -14355,13 +14354,13 @@
         <v>34</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>36</v>
@@ -14410,7 +14409,7 @@
         <v>36</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>584</v>
@@ -14447,7 +14446,7 @@
         <v>36</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y100" t="s" s="2">
         <v>588</v>
@@ -14480,10 +14479,10 @@
         <v>35</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>36</v>
@@ -14520,7 +14519,7 @@
         <v>34</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>36</v>
@@ -14532,13 +14531,13 @@
         <v>36</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14589,13 +14588,13 @@
         <v>36</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>36</v>
@@ -14613,7 +14612,7 @@
         <v>36</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>36</v>
@@ -14631,7 +14630,7 @@
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14650,16 +14649,16 @@
         <v>36</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14697,19 +14696,19 @@
         <v>36</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>34</v>
@@ -14718,10 +14717,10 @@
         <v>35</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>36</v>
@@ -14733,7 +14732,7 @@
         <v>36</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>36</v>
@@ -14767,22 +14766,22 @@
         <v>36</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>36</v>
@@ -14831,7 +14830,7 @@
         <v>36</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>34</v>
@@ -14840,10 +14839,10 @@
         <v>35</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>36</v>
@@ -14852,10 +14851,10 @@
         <v>36</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>36</v>
@@ -14880,7 +14879,7 @@
         <v>34</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>36</v>
@@ -14892,13 +14891,13 @@
         <v>36</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14949,13 +14948,13 @@
         <v>36</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>36</v>
@@ -14973,7 +14972,7 @@
         <v>36</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>36</v>
@@ -14991,7 +14990,7 @@
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15010,16 +15009,16 @@
         <v>36</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15057,19 +15056,19 @@
         <v>36</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>34</v>
@@ -15078,10 +15077,10 @@
         <v>35</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>36</v>
@@ -15093,7 +15092,7 @@
         <v>36</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>36</v>
@@ -15115,10 +15114,10 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>36</v>
@@ -15127,22 +15126,22 @@
         <v>36</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>36</v>
@@ -15191,19 +15190,19 @@
         <v>36</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>36</v>
@@ -15212,10 +15211,10 @@
         <v>36</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>36</v>
@@ -15240,7 +15239,7 @@
         <v>34</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>36</v>
@@ -15249,19 +15248,19 @@
         <v>36</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15311,19 +15310,19 @@
         <v>36</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>36</v>
@@ -15332,10 +15331,10 @@
         <v>36</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>36</v>
@@ -15357,10 +15356,10 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>36</v>
@@ -15369,22 +15368,22 @@
         <v>36</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>36</v>
@@ -15433,19 +15432,19 @@
         <v>36</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>36</v>
@@ -15454,10 +15453,10 @@
         <v>36</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>36</v>
@@ -15482,7 +15481,7 @@
         <v>34</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>36</v>
@@ -15491,22 +15490,22 @@
         <v>36</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>36</v>
@@ -15555,19 +15554,19 @@
         <v>36</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>36</v>
@@ -15576,10 +15575,10 @@
         <v>36</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>36</v>
@@ -15604,7 +15603,7 @@
         <v>34</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>36</v>
@@ -15613,22 +15612,22 @@
         <v>36</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>36</v>
@@ -15677,19 +15676,19 @@
         <v>36</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>36</v>
@@ -15698,10 +15697,10 @@
         <v>36</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>36</v>
@@ -15726,7 +15725,7 @@
         <v>34</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>36</v>
@@ -15735,22 +15734,22 @@
         <v>36</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>36</v>
@@ -15799,19 +15798,19 @@
         <v>36</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>36</v>
@@ -15820,10 +15819,10 @@
         <v>36</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>36</v>
@@ -15848,7 +15847,7 @@
         <v>34</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>36</v>
@@ -15927,10 +15926,10 @@
         <v>34</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>606</v>
@@ -15970,7 +15969,7 @@
         <v>34</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>36</v>
@@ -15982,7 +15981,7 @@
         <v>36</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>610</v>
@@ -15991,7 +15990,7 @@
         <v>611</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16047,13 +16046,13 @@
         <v>34</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>36</v>
@@ -16099,7 +16098,7 @@
         <v>36</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K114" t="s" s="2">
         <v>614</v>
@@ -16170,10 +16169,10 @@
         <v>35</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>36</v>
@@ -16219,7 +16218,7 @@
         <v>36</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>621</v>
@@ -16290,10 +16289,10 @@
         <v>35</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>36</v>
@@ -16333,13 +16332,13 @@
         <v>35</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>546</v>
@@ -16412,7 +16411,7 @@
         <v>35</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>630</v>
@@ -16452,7 +16451,7 @@
         <v>34</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>36</v>
@@ -16464,13 +16463,13 @@
         <v>36</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16521,13 +16520,13 @@
         <v>36</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>36</v>
@@ -16545,7 +16544,7 @@
         <v>36</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>36</v>
@@ -16563,7 +16562,7 @@
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16582,16 +16581,16 @@
         <v>36</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16629,19 +16628,19 @@
         <v>36</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>34</v>
@@ -16650,10 +16649,10 @@
         <v>35</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>36</v>
@@ -16665,7 +16664,7 @@
         <v>36</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>36</v>
@@ -16696,13 +16695,13 @@
         <v>36</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>558</v>
@@ -16711,10 +16710,10 @@
         <v>559</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>36</v>
@@ -16772,10 +16771,10 @@
         <v>35</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>36</v>
@@ -16787,7 +16786,7 @@
         <v>36</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>36</v>
@@ -16809,22 +16808,22 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>637</v>
@@ -16861,13 +16860,13 @@
         <v>36</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>36</v>
@@ -16888,16 +16887,16 @@
         <v>636</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>36</v>
@@ -16906,13 +16905,13 @@
         <v>641</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>36</v>
@@ -16934,16 +16933,16 @@
         <v>34</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K121" t="s" s="2">
         <v>643</v>
@@ -16958,7 +16957,7 @@
         <v>646</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>36</v>
@@ -16983,7 +16982,7 @@
         <v>36</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y121" t="s" s="2">
         <v>647</v>
@@ -17013,13 +17012,13 @@
         <v>34</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>649</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>36</v>
@@ -17028,16 +17027,16 @@
         <v>650</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="122" hidden="true">
@@ -17056,10 +17055,10 @@
         <v>34</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>36</v>
@@ -17068,7 +17067,7 @@
         <v>36</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L122" t="s" s="2">
         <v>652</v>
@@ -17080,7 +17079,7 @@
         <v>654</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>36</v>
@@ -17105,13 +17104,13 @@
         <v>36</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>36</v>
@@ -17135,13 +17134,13 @@
         <v>34</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>655</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>36</v>
@@ -17150,10 +17149,10 @@
         <v>36</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>36</v>
@@ -17171,7 +17170,7 @@
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17190,19 +17189,19 @@
         <v>36</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>36</v>
@@ -17227,13 +17226,13 @@
         <v>36</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>486</v>
+        <v>657</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>657</v>
+        <v>487</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>36</v>
@@ -17260,10 +17259,10 @@
         <v>35</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>36</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:09:26+00:00</t>
+    <t>2023-09-19T16:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:18:04+00:00</t>
+    <t>2023-09-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:08:45+00:00</t>
+    <t>2023-09-27T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:45:14+00:00</t>
+    <t>2023-11-23T10:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-23T10:14:09+00:00</t>
+    <t>2023-11-28T12:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,6 +443,9 @@
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
 This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
   </si>
@@ -681,10 +684,6 @@
   </si>
   <si>
     <t>Moment de la mesure</t>
-  </si>
-  <si>
-    <t>Moment de la mesure
-Texte libre</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -3572,10 +3571,10 @@
         <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3625,7 +3624,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3660,10 +3659,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3686,16 +3685,16 @@
         <v>92</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3745,7 +3744,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3780,10 +3779,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3806,16 +3805,16 @@
         <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3841,13 +3840,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3865,7 +3864,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3886,10 +3885,10 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>80</v>
@@ -3900,10 +3899,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3926,16 +3925,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3961,13 +3960,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3985,7 +3984,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -4006,10 +4005,10 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -4020,10 +4019,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4049,13 +4048,13 @@
         <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4105,7 +4104,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -4140,10 +4139,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4166,16 +4165,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4201,13 +4200,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -4225,7 +4224,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4260,14 +4259,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4286,16 +4285,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4345,7 +4344,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4369,7 +4368,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -4380,14 +4379,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4406,16 +4405,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4465,7 +4464,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4500,10 +4499,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4532,7 +4531,7 @@
         <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>117</v>
@@ -4585,7 +4584,7 @@
         <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4620,13 +4619,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
@@ -4648,13 +4647,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4705,7 +4704,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4740,13 +4739,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>80</v>
@@ -4768,13 +4767,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4825,7 +4824,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4860,13 +4859,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>113</v>
@@ -4888,13 +4887,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>117</v>
@@ -4947,7 +4946,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4982,13 +4981,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
@@ -5010,10 +5009,10 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>213</v>
@@ -5067,7 +5066,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5612,7 +5611,7 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>249</v>
@@ -5771,7 +5770,7 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y27" t="s" s="2">
         <v>267</v>
@@ -5893,7 +5892,7 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y28" t="s" s="2">
         <v>267</v>
@@ -6216,7 +6215,7 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>281</v>
@@ -6818,7 +6817,7 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>312</v>
@@ -7343,7 +7342,7 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y40" t="s" s="2">
         <v>353</v>
@@ -7666,7 +7665,7 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>281</v>
@@ -7788,7 +7787,7 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>281</v>
@@ -8390,7 +8389,7 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>312</v>
@@ -10210,7 +10209,7 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>470</v>
@@ -10578,7 +10577,7 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>499</v>
@@ -10737,7 +10736,7 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y68" t="s" s="2">
         <v>510</v>
@@ -11060,7 +11059,7 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>281</v>
@@ -11662,7 +11661,7 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>312</v>
@@ -12187,7 +12186,7 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
@@ -12427,7 +12426,7 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y82" t="s" s="2">
         <v>548</v>
@@ -12750,7 +12749,7 @@
         <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>281</v>
@@ -12787,7 +12786,7 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
@@ -13352,7 +13351,7 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>281</v>
@@ -13389,7 +13388,7 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
@@ -14593,7 +14592,7 @@
         <v>80</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y100" t="s" s="2">
         <v>623</v>
@@ -15038,7 +15037,7 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>281</v>
@@ -15640,7 +15639,7 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>312</v>
@@ -17129,7 +17128,7 @@
         <v>80</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y121" t="s" s="2">
         <v>353</v>
@@ -17373,7 +17372,7 @@
         <v>80</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y123" t="s" s="2">
         <v>510</v>
@@ -17495,7 +17494,7 @@
         <v>80</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y124" t="s" s="2">
         <v>701</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4834" uniqueCount="706">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:14:54+00:00</t>
+    <t>2023-11-28T12:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1756,6 +1756,9 @@
   </si>
   <si>
     <t>Méthode de la mesure</t>
+  </si>
+  <si>
+    <t>Indicates the mechanism used to perform the observation.</t>
   </si>
   <si>
     <t>Only used if not implicit in code for Observation.code.</t>
@@ -12982,7 +12985,7 @@
         <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
@@ -12997,13 +13000,13 @@
         <v>560</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -13028,13 +13031,11 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -13073,10 +13074,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13087,10 +13088,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13205,10 +13206,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13325,10 +13326,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13392,7 +13393,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13445,10 +13446,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13567,10 +13568,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13593,16 +13594,16 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13652,7 +13653,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13670,27 +13671,27 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13713,16 +13714,16 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13772,7 +13773,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13790,27 +13791,27 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13833,19 +13834,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13894,7 +13895,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13906,7 +13907,7 @@
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
@@ -13915,10 +13916,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13929,10 +13930,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14047,10 +14048,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14167,14 +14168,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14196,10 +14197,10 @@
         <v>114</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>117</v>
@@ -14254,7 +14255,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14289,10 +14290,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14315,16 +14316,16 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14374,7 +14375,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14383,10 +14384,10 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>80</v>
@@ -14395,10 +14396,10 @@
         <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -14409,10 +14410,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14435,16 +14436,16 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14494,7 +14495,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14503,10 +14504,10 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>80</v>
@@ -14515,10 +14516,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14529,10 +14530,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14558,16 +14559,16 @@
         <v>262</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14595,10 +14596,10 @@
         <v>175</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
@@ -14616,7 +14617,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14634,10 +14635,10 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>534</v>
@@ -14651,10 +14652,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14680,16 +14681,16 @@
         <v>262</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14717,10 +14718,10 @@
         <v>253</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14738,7 +14739,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14756,10 +14757,10 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>534</v>
@@ -14773,10 +14774,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14891,10 +14892,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15011,10 +15012,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15133,10 +15134,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15251,10 +15252,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15371,10 +15372,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15493,10 +15494,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15613,10 +15614,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15735,10 +15736,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15857,10 +15858,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15979,10 +15980,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16101,10 +16102,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16127,19 +16128,19 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16188,7 +16189,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16200,7 +16201,7 @@
         <v>103</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>80</v>
@@ -16209,10 +16210,10 @@
         <v>80</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -16223,10 +16224,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16252,10 +16253,10 @@
         <v>107</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>314</v>
@@ -16308,7 +16309,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16329,10 +16330,10 @@
         <v>80</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16343,10 +16344,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16369,16 +16370,16 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16428,7 +16429,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16449,10 +16450,10 @@
         <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
@@ -16463,10 +16464,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16489,16 +16490,16 @@
         <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16548,7 +16549,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16569,10 +16570,10 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
@@ -16583,10 +16584,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16609,19 +16610,19 @@
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -16670,7 +16671,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16682,7 +16683,7 @@
         <v>103</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>80</v>
@@ -16691,10 +16692,10 @@
         <v>80</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -16705,10 +16706,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16823,10 +16824,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16943,14 +16944,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16972,10 +16973,10 @@
         <v>114</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>117</v>
@@ -17030,7 +17031,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -17065,10 +17066,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17094,16 +17095,16 @@
         <v>262</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -17152,7 +17153,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>91</v>
@@ -17170,7 +17171,7 @@
         <v>80</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>357</v>
@@ -17187,10 +17188,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17213,16 +17214,16 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>444</v>
@@ -17253,10 +17254,10 @@
         <v>253</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>80</v>
@@ -17274,7 +17275,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17283,7 +17284,7 @@
         <v>91</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>104</v>
@@ -17292,7 +17293,7 @@
         <v>80</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>449</v>
@@ -17309,10 +17310,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17338,13 +17339,13 @@
         <v>262</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>509</v>
@@ -17396,7 +17397,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17405,7 +17406,7 @@
         <v>91</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>104</v>
@@ -17431,10 +17432,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17497,7 +17498,7 @@
         <v>151</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="Z124" t="s" s="2">
         <v>531</v>
@@ -17518,7 +17519,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17553,10 +17554,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17582,16 +17583,16 @@
         <v>81</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17640,7 +17641,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17661,10 +17662,10 @@
         <v>80</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4834" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="705">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:15:35+00:00</t>
+    <t>2023-11-28T12:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1756,9 +1756,6 @@
   </si>
   <si>
     <t>Méthode de la mesure</t>
-  </si>
-  <si>
-    <t>Indicates the mechanism used to perform the observation.</t>
   </si>
   <si>
     <t>Only used if not implicit in code for Observation.code.</t>
@@ -12985,7 +12982,7 @@
         <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
@@ -13000,13 +12997,13 @@
         <v>560</v>
       </c>
       <c r="M87" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -13031,11 +13028,13 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -13074,10 +13073,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13088,10 +13087,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13206,10 +13205,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13326,10 +13325,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13393,7 +13392,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13446,10 +13445,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13568,10 +13567,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13594,16 +13593,16 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13653,7 +13652,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13671,27 +13670,27 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>580</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13714,16 +13713,16 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13773,7 +13772,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13791,27 +13790,27 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>589</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13834,19 +13833,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13895,7 +13894,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13907,19 +13906,19 @@
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AK94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13930,10 +13929,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14048,10 +14047,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14168,14 +14167,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14197,10 +14196,10 @@
         <v>114</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>117</v>
@@ -14255,7 +14254,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14290,10 +14289,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14316,16 +14315,16 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14375,7 +14374,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14384,22 +14383,22 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="AJ98" t="s" s="2">
+      <c r="AK98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="AK98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AN98" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -14410,10 +14409,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14436,16 +14435,16 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M99" t="s" s="2">
-        <v>617</v>
-      </c>
       <c r="N99" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14495,7 +14494,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14504,22 +14503,22 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="AJ99" t="s" s="2">
+      <c r="AK99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="AK99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>613</v>
-      </c>
       <c r="AN99" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14530,10 +14529,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14559,16 +14558,16 @@
         <v>262</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14596,11 +14595,11 @@
         <v>175</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="Z100" t="s" s="2">
-        <v>625</v>
-      </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
       </c>
@@ -14617,7 +14616,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14635,10 +14634,10 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>534</v>
@@ -14652,10 +14651,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14681,16 +14680,16 @@
         <v>262</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14718,10 +14717,10 @@
         <v>253</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14739,7 +14738,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14757,10 +14756,10 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>534</v>
@@ -14774,10 +14773,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14892,10 +14891,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15012,10 +15011,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15134,10 +15133,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15252,10 +15251,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15372,10 +15371,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15494,10 +15493,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15614,10 +15613,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15736,10 +15735,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15858,10 +15857,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15980,10 +15979,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16102,10 +16101,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16128,19 +16127,19 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16189,7 +16188,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16201,19 +16200,19 @@
         <v>103</v>
       </c>
       <c r="AJ113" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM113" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="AK113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM113" t="s" s="2">
+      <c r="AN113" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -16224,10 +16223,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16253,10 +16252,10 @@
         <v>107</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>314</v>
@@ -16309,7 +16308,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16330,10 +16329,10 @@
         <v>80</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16344,10 +16343,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16370,16 +16369,16 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16429,7 +16428,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16450,10 +16449,10 @@
         <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
@@ -16464,10 +16463,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16490,16 +16489,16 @@
         <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16549,7 +16548,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16570,10 +16569,10 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
@@ -16584,10 +16583,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16610,19 +16609,19 @@
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M117" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -16671,7 +16670,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16683,19 +16682,19 @@
         <v>103</v>
       </c>
       <c r="AJ117" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM117" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="AK117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM117" t="s" s="2">
+      <c r="AN117" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -16706,10 +16705,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16824,10 +16823,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16944,14 +16943,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16973,10 +16972,10 @@
         <v>114</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>117</v>
@@ -17031,7 +17030,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -17066,10 +17065,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17095,16 +17094,16 @@
         <v>262</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="N121" t="s" s="2">
+      <c r="O121" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -17153,7 +17152,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>91</v>
@@ -17171,7 +17170,7 @@
         <v>80</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>357</v>
@@ -17188,10 +17187,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17214,16 +17213,16 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>444</v>
@@ -17254,37 +17253,37 @@
         <v>253</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="Z122" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="Z122" t="s" s="2">
+      <c r="AA122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI122" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>104</v>
@@ -17293,7 +17292,7 @@
         <v>80</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>449</v>
@@ -17310,10 +17309,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17339,13 +17338,13 @@
         <v>262</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>509</v>
@@ -17397,7 +17396,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17406,7 +17405,7 @@
         <v>91</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>104</v>
@@ -17432,10 +17431,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17498,7 +17497,7 @@
         <v>151</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="Z124" t="s" s="2">
         <v>531</v>
@@ -17519,7 +17518,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17554,10 +17553,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17583,16 +17582,16 @@
         <v>81</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="M125" t="s" s="2">
-        <v>705</v>
-      </c>
       <c r="N125" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="O125" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17641,7 +17640,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17662,10 +17661,10 @@
         <v>80</v>
       </c>
       <c r="AM125" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4834" uniqueCount="706">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:22:20+00:00</t>
+    <t>2023-11-28T12:44:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1756,6 +1756,9 @@
   </si>
   <si>
     <t>Méthode de la mesure</t>
+  </si>
+  <si>
+    <t>Indicates the mechanism used to perform the observation.</t>
   </si>
   <si>
     <t>Only used if not implicit in code for Observation.code.</t>
@@ -12982,7 +12985,7 @@
         <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
@@ -12997,13 +13000,13 @@
         <v>560</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -13028,13 +13031,11 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -13073,10 +13074,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13087,10 +13088,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13205,10 +13206,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13325,10 +13326,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13392,7 +13393,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13445,10 +13446,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13567,10 +13568,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13593,16 +13594,16 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13652,7 +13653,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13670,27 +13671,27 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13713,16 +13714,16 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13772,7 +13773,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13790,27 +13791,27 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13833,19 +13834,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13894,7 +13895,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13906,7 +13907,7 @@
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
@@ -13915,10 +13916,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13929,10 +13930,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14047,10 +14048,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14167,14 +14168,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14196,10 +14197,10 @@
         <v>114</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>117</v>
@@ -14254,7 +14255,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14289,10 +14290,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14315,16 +14316,16 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14374,7 +14375,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14383,10 +14384,10 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>80</v>
@@ -14395,10 +14396,10 @@
         <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -14409,10 +14410,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14435,16 +14436,16 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14494,7 +14495,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14503,10 +14504,10 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>80</v>
@@ -14515,10 +14516,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14529,10 +14530,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14558,16 +14559,16 @@
         <v>262</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14595,10 +14596,10 @@
         <v>175</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
@@ -14616,7 +14617,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14634,10 +14635,10 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>534</v>
@@ -14651,10 +14652,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14680,16 +14681,16 @@
         <v>262</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14717,10 +14718,10 @@
         <v>253</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14738,7 +14739,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14756,10 +14757,10 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>534</v>
@@ -14773,10 +14774,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14891,10 +14892,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15011,10 +15012,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15133,10 +15134,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15251,10 +15252,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15371,10 +15372,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15493,10 +15494,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15613,10 +15614,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15735,10 +15736,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15857,10 +15858,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15979,10 +15980,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16101,10 +16102,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16127,19 +16128,19 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16188,7 +16189,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16200,7 +16201,7 @@
         <v>103</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>80</v>
@@ -16209,10 +16210,10 @@
         <v>80</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -16223,10 +16224,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16252,10 +16253,10 @@
         <v>107</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>314</v>
@@ -16308,7 +16309,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16329,10 +16330,10 @@
         <v>80</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16343,10 +16344,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16369,16 +16370,16 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16428,7 +16429,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16449,10 +16450,10 @@
         <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
@@ -16463,10 +16464,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16489,16 +16490,16 @@
         <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16548,7 +16549,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16569,10 +16570,10 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
@@ -16583,10 +16584,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16609,19 +16610,19 @@
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -16670,7 +16671,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16682,7 +16683,7 @@
         <v>103</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>80</v>
@@ -16691,10 +16692,10 @@
         <v>80</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -16705,10 +16706,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16823,10 +16824,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16943,14 +16944,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16972,10 +16973,10 @@
         <v>114</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>117</v>
@@ -17030,7 +17031,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -17065,10 +17066,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17094,16 +17095,16 @@
         <v>262</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -17152,7 +17153,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>91</v>
@@ -17170,7 +17171,7 @@
         <v>80</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>357</v>
@@ -17187,10 +17188,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17213,16 +17214,16 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>444</v>
@@ -17253,10 +17254,10 @@
         <v>253</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>80</v>
@@ -17274,7 +17275,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17283,7 +17284,7 @@
         <v>91</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>104</v>
@@ -17292,7 +17293,7 @@
         <v>80</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>449</v>
@@ -17309,10 +17310,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17338,13 +17339,13 @@
         <v>262</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>509</v>
@@ -17396,7 +17397,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17405,7 +17406,7 @@
         <v>91</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>104</v>
@@ -17431,10 +17432,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17497,7 +17498,7 @@
         <v>151</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="Z124" t="s" s="2">
         <v>531</v>
@@ -17518,7 +17519,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17553,10 +17554,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17582,16 +17583,16 @@
         <v>81</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17640,7 +17641,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17661,10 +17662,10 @@
         <v>80</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:44:29+00:00</t>
+    <t>2023-11-28T13:07:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:07:26+00:00</t>
+    <t>2023-11-28T13:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1826,12 +1826,11 @@
 </t>
   </si>
   <si>
-    <t>Dispositif utilisé pour l'observation</t>
-  </si>
-  <si>
     <t>Dispositif utilisé pour l'observation
-Si la mesure a été faite par un objet connecté (Profil PhdDevice)
-=&gt;cette référence est obligatoire</t>
+Si la mesure a été faite par un objet connecté (Profil PhdDevice), cette référence est obligatoire</t>
+  </si>
+  <si>
+    <t>The device used to generate the observation data.</t>
   </si>
   <si>
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
@@ -13705,7 +13704,7 @@
         <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:18:47+00:00</t>
+    <t>2023-11-28T13:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:27:45+00:00</t>
+    <t>2023-11-28T13:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:42:11+00:00</t>
+    <t>2023-12-08T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T10:33:05+00:00</t>
+    <t>2023-12-29T10:04:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:04:05+00:00</t>
+    <t>2024-02-01T10:35:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T10:35:02+00:00</t>
+    <t>2024-02-01T13:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:55:30+00:00</t>
+    <t>2024-02-01T13:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:56:11+00:00</t>
+    <t>2024-02-01T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:29:51+00:00</t>
+    <t>2024-02-01T16:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T16:04:25+00:00</t>
+    <t>2024-02-05T14:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:48:49+00:00</t>
+    <t>2024-02-12T14:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:46:58+00:00</t>
+    <t>2024-02-12T14:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:53:29+00:00</t>
+    <t>2024-04-08T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
